--- a/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_9_47.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_9_47.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4292602.704160015</v>
+        <v>4328920.152355723</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13275569.19337385</v>
+        <v>13279501.51514058</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13275569.19337385</v>
+        <v>13279501.51514058</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.5370116996959</v>
+        <v>987.0883260126911</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.5370116996959</v>
+        <v>987.0883260126911</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20558356.68881374</v>
+        <v>20557546.73593489</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557451</v>
+        <v>80.07191941636594</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -669,10 +669,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H2" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -702,16 +702,16 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.798687867826661</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>120.5997139955137</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -751,10 +751,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,28 +778,28 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>133.6519859716245</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S3" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T3" t="n">
-        <v>126.6547001872139</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U3" t="n">
-        <v>374</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V3" t="n">
-        <v>14.51066719152016</v>
+        <v>373</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>19.86273944538755</v>
+        <v>373</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N4" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O4" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P4" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,13 +906,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8805867536895</v>
+        <v>186.8163952245313</v>
       </c>
       <c r="U5" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -982,16 +982,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I6" t="n">
-        <v>23.24960267314763</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,19 +1015,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>137.3421578965963</v>
       </c>
       <c r="R6" t="n">
-        <v>133.6519859716245</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S6" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T6" t="n">
-        <v>4.473444462796863</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1959257979225981</v>
+        <v>374</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N7" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O7" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P7" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q7" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1143,13 +1143,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H8" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I8" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>85.50414770182039</v>
+        <v>87.36594612241093</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U8" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1213,19 +1213,19 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>154.6928956836637</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1252,22 +1252,22 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>153.1291859623778</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S9" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T9" t="n">
-        <v>4.473444462796863</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>374</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N10" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O10" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P10" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q10" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S11" t="n">
         <v>142.3350019731772</v>
@@ -1422,7 +1422,7 @@
         <v>259.6218731858503</v>
       </c>
       <c r="U11" t="n">
-        <v>328.5712507480957</v>
+        <v>328.1106633827815</v>
       </c>
       <c r="V11" t="n">
         <v>308.8510241668239</v>
@@ -1444,13 +1444,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C12" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
         <v>21.67209722191262</v>
@@ -1498,7 +1498,7 @@
         <v>305.4120422616786</v>
       </c>
       <c r="T12" t="n">
-        <v>402.3753501231742</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U12" t="n">
         <v>79.16168051490372</v>
@@ -1510,7 +1510,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y12" t="n">
         <v>399.3913927661343</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M13" t="n">
         <v>102.3923982877958</v>
@@ -1574,7 +1574,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S13" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1617,13 +1617,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H14" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T14" t="n">
         <v>259.6218731858503</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C15" t="n">
         <v>40.09991244551929</v>
@@ -1696,10 +1696,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>3.999611346725456</v>
+        <v>177.5914272286983</v>
       </c>
       <c r="H15" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1732,19 +1732,19 @@
         <v>180.333570877285</v>
       </c>
       <c r="S15" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T15" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U15" t="n">
-        <v>252.7534963968768</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V15" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X15" t="n">
         <v>419.8627394453875</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M16" t="n">
         <v>102.3923982877958</v>
@@ -1802,13 +1802,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P16" t="n">
-        <v>290.5838154131063</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q16" t="n">
-        <v>352.895266425598</v>
+        <v>352.0570205760006</v>
       </c>
       <c r="R16" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S16" t="n">
         <v>30.56285675203577</v>
@@ -1854,10 +1854,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H17" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>142.3350019731772</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>237.1483725282999</v>
       </c>
       <c r="C18" t="n">
         <v>361.0999124455193</v>
@@ -1933,10 +1933,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>177.5914272286983</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H18" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1966,16 +1966,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S18" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T18" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U18" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V18" t="n">
         <v>93.51066719152016</v>
@@ -2027,10 +2027,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M19" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N19" t="n">
         <v>155.2579933044718</v>
@@ -2039,16 +2039,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P19" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q19" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S19" t="n">
-        <v>29.72461090244146</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S20" t="n">
         <v>142.3350019731772</v>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C21" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E21" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>192.2280582198497</v>
+        <v>192.2280582198499</v>
       </c>
       <c r="G21" t="n">
         <v>3.99961134672543</v>
@@ -2206,7 +2206,7 @@
         <v>180.333570877285</v>
       </c>
       <c r="S21" t="n">
-        <v>131.8202263797057</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T21" t="n">
         <v>81.3753501231742</v>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>9.483546242607703</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M22" t="n">
         <v>102.3923982877958</v>
@@ -2282,7 +2282,7 @@
         <v>352.895266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>377.7099312598395</v>
+        <v>376.871685410242</v>
       </c>
       <c r="S22" t="n">
         <v>30.56285675203577</v>
@@ -2328,10 +2328,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H23" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S23" t="n">
         <v>142.3350019731772</v>
@@ -2404,16 +2404,16 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F24" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>3.999611346725456</v>
+        <v>306.9405130354632</v>
       </c>
       <c r="H24" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2440,16 +2440,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>501.333570877285</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S24" t="n">
         <v>452.8202263797057</v>
       </c>
       <c r="T24" t="n">
-        <v>402.3753501231742</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U24" t="n">
-        <v>252.7534963968771</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V24" t="n">
         <v>93.51066719152016</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M25" t="n">
         <v>102.3923982877958</v>
@@ -2513,16 +2513,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P25" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q25" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S25" t="n">
-        <v>29.72461090244517</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H26" t="n">
         <v>72.84688483418068</v>
@@ -2598,10 +2598,10 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T26" t="n">
         <v>259.6218731858503</v>
@@ -2632,22 +2632,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E27" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F27" t="n">
-        <v>192.22805821985</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>324.9996113467254</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H27" t="n">
-        <v>4.021973978873961</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2680,13 +2680,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S27" t="n">
-        <v>131.8202263797056</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T27" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16168051490372</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V27" t="n">
         <v>93.51066719152016</v>
@@ -2698,7 +2698,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y27" t="n">
-        <v>78.39139276613435</v>
+        <v>251.9832086481073</v>
       </c>
     </row>
     <row r="28">
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>10.3217920922054</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M28" t="n">
         <v>102.3923982877958</v>
@@ -2750,13 +2750,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P28" t="n">
-        <v>290.5838154131063</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q28" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S28" t="n">
         <v>30.56285675203577</v>
@@ -2805,10 +2805,10 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H29" t="n">
-        <v>73.30747219949504</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C30" t="n">
         <v>40.09991244551929</v>
@@ -2878,7 +2878,7 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F30" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
         <v>3.99961134672543</v>
@@ -2923,16 +2923,16 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U30" t="n">
-        <v>252.7534963968766</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V30" t="n">
         <v>414.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>419.8627394453875</v>
+        <v>272.4545553273603</v>
       </c>
       <c r="Y30" t="n">
         <v>78.39139276613435</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>9.483546242607703</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M31" t="n">
         <v>102.3923982877958</v>
@@ -2996,7 +2996,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S31" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3081,10 +3081,10 @@
         <v>259.6218731858503</v>
       </c>
       <c r="U32" t="n">
-        <v>328.1106633827815</v>
+        <v>328.5712507480957</v>
       </c>
       <c r="V32" t="n">
-        <v>309.311611532138</v>
+        <v>308.8510241668239</v>
       </c>
       <c r="W32" t="n">
         <v>317.3734759809475</v>
@@ -3109,19 +3109,19 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>306.940513035463</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H33" t="n">
-        <v>325.021973978874</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I33" t="n">
         <v>191.6509141932353</v>
@@ -3157,7 +3157,7 @@
         <v>131.8202263797056</v>
       </c>
       <c r="T33" t="n">
-        <v>81.3753501231742</v>
+        <v>384.3162518119123</v>
       </c>
       <c r="U33" t="n">
         <v>79.16168051490372</v>
@@ -3230,10 +3230,10 @@
         <v>352.895266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>376.8716854102422</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S34" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3279,7 +3279,7 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H35" t="n">
-        <v>73.30747219949504</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S35" t="n">
         <v>142.3350019731772</v>
@@ -3340,19 +3340,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C36" t="n">
-        <v>213.6917283274922</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G36" t="n">
         <v>3.99961134672543</v>
@@ -3397,13 +3397,13 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U36" t="n">
-        <v>79.16168051490371</v>
+        <v>252.7534963968768</v>
       </c>
       <c r="V36" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X36" t="n">
         <v>98.86273944538755</v>
@@ -3504,7 +3504,7 @@
         <v>128.4745782429939</v>
       </c>
       <c r="D38" t="n">
-        <v>89.33915573984979</v>
+        <v>89.79974310516393</v>
       </c>
       <c r="E38" t="n">
         <v>83.36328960686865</v>
@@ -3519,7 +3519,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C39" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>26.93768689770263</v>
+        <v>200.5295027796759</v>
       </c>
       <c r="E39" t="n">
         <v>21.67209722191262</v>
@@ -3592,7 +3592,7 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G39" t="n">
-        <v>3.999611346725456</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H39" t="n">
         <v>4.021973978873961</v>
@@ -3640,13 +3640,13 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>272.4545553273608</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="40">
@@ -3750,13 +3750,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H41" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3817,7 +3817,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D42" t="n">
         <v>26.93768689770263</v>
@@ -3829,13 +3829,13 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>324.9996113467254</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H42" t="n">
-        <v>325.021973978874</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I42" t="n">
-        <v>94.96326777262608</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3859,25 +3859,25 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>501.333570877285</v>
+        <v>353.9253867592579</v>
       </c>
       <c r="S42" t="n">
-        <v>131.8202263797056</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T42" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U42" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V42" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>98.86273944538755</v>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M43" t="n">
         <v>102.3923982877958</v>
@@ -3935,16 +3935,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P43" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q43" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S43" t="n">
-        <v>29.7246109025154</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3987,13 +3987,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H44" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>142.3350019731772</v>
@@ -4051,28 +4051,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C45" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E45" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G45" t="n">
-        <v>3.99961134672543</v>
+        <v>177.5914272286986</v>
       </c>
       <c r="H45" t="n">
-        <v>306.9628756676116</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I45" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4102,13 +4102,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S45" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T45" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U45" t="n">
-        <v>79.16168051490371</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V45" t="n">
         <v>93.51066719152016</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M46" t="n">
         <v>102.3923982877958</v>
@@ -4172,16 +4172,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P46" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q46" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S46" t="n">
-        <v>29.7246109025261</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.914147375084</v>
+        <v>106.7884999460195</v>
       </c>
       <c r="C2" t="n">
-        <v>56.9398259175144</v>
+        <v>56.81417848844992</v>
       </c>
       <c r="D2" t="n">
-        <v>46.49623426110047</v>
+        <v>46.37058683203599</v>
       </c>
       <c r="E2" t="n">
-        <v>42.08887102183921</v>
+        <v>41.96322359277473</v>
       </c>
       <c r="F2" t="n">
-        <v>37.14985212485754</v>
+        <v>37.02420469579306</v>
       </c>
       <c r="G2" t="n">
-        <v>33.76871875540306</v>
+        <v>33.64713203391685</v>
       </c>
       <c r="H2" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="I2" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>29.93969029977264</v>
       </c>
       <c r="K2" t="n">
-        <v>81.5583303517588</v>
+        <v>399.2096902997726</v>
       </c>
       <c r="L2" t="n">
-        <v>145.6202453266332</v>
+        <v>463.8996632645968</v>
       </c>
       <c r="M2" t="n">
-        <v>515.8802453266331</v>
+        <v>833.1696632645967</v>
       </c>
       <c r="N2" t="n">
-        <v>515.8802453266331</v>
+        <v>1064.065793611129</v>
       </c>
       <c r="O2" t="n">
-        <v>755.48</v>
+        <v>1064.065793611129</v>
       </c>
       <c r="P2" t="n">
-        <v>1125.74</v>
+        <v>1122.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="R2" t="n">
-        <v>1494.183143567852</v>
+        <v>1492</v>
       </c>
       <c r="S2" t="n">
-        <v>1407.815317606417</v>
+        <v>1405.724707412506</v>
       </c>
       <c r="T2" t="n">
-        <v>1221.067250178448</v>
+        <v>1218.994415731961</v>
       </c>
       <c r="U2" t="n">
-        <v>969.3617021698518</v>
+        <v>967.2891925799706</v>
       </c>
       <c r="V2" t="n">
-        <v>737.1889504861913</v>
+        <v>735.1164408963101</v>
       </c>
       <c r="W2" t="n">
-        <v>496.4076616165473</v>
+        <v>494.3351520266661</v>
       </c>
       <c r="X2" t="n">
-        <v>302.1835874138526</v>
+        <v>300.1110778239714</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.7417362190987</v>
+        <v>187.6692266292175</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>578.2064886541781</v>
+        <v>381.2922089875784</v>
       </c>
       <c r="C3" t="n">
-        <v>578.2064886541781</v>
+        <v>381.2922089875784</v>
       </c>
       <c r="D3" t="n">
-        <v>578.2064886541781</v>
+        <v>29.84</v>
       </c>
       <c r="E3" t="n">
-        <v>578.2064886541781</v>
+        <v>29.84</v>
       </c>
       <c r="F3" t="n">
-        <v>578.2064886541781</v>
+        <v>29.84</v>
       </c>
       <c r="G3" t="n">
-        <v>578.2064886541781</v>
+        <v>29.84</v>
       </c>
       <c r="H3" t="n">
-        <v>244.8234770117097</v>
+        <v>29.84</v>
       </c>
       <c r="I3" t="n">
-        <v>33.13396963146437</v>
+        <v>29.84</v>
       </c>
       <c r="J3" t="n">
-        <v>177.6113405614803</v>
+        <v>174.5185557413367</v>
       </c>
       <c r="K3" t="n">
-        <v>401.8775591086939</v>
+        <v>399.1286311753428</v>
       </c>
       <c r="L3" t="n">
-        <v>720.3885386284223</v>
+        <v>718.1019687139392</v>
       </c>
       <c r="M3" t="n">
-        <v>861.5031803712816</v>
+        <v>859.7561604567984</v>
       </c>
       <c r="N3" t="n">
-        <v>1051.274153846774</v>
+        <v>1050.08096421531</v>
       </c>
       <c r="O3" t="n">
-        <v>1341.994549492757</v>
+        <v>1337.587921002191</v>
       </c>
       <c r="P3" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="Q3" t="n">
-        <v>1349.46108157432</v>
+        <v>1492</v>
       </c>
       <c r="R3" t="n">
-        <v>1214.459075542376</v>
+        <v>1357.132890099179</v>
       </c>
       <c r="S3" t="n">
-        <v>1151.339064143017</v>
+        <v>1294.053235093949</v>
       </c>
       <c r="T3" t="n">
-        <v>1023.405023549871</v>
+        <v>1289.54336170862</v>
       </c>
       <c r="U3" t="n">
-        <v>645.6272457720935</v>
+        <v>1289.345599801055</v>
       </c>
       <c r="V3" t="n">
-        <v>630.9700061846994</v>
+        <v>912.5779230333786</v>
       </c>
       <c r="W3" t="n">
-        <v>598.2698618313373</v>
+        <v>879.8777786800165</v>
       </c>
       <c r="X3" t="n">
-        <v>578.2064886541781</v>
+        <v>503.1101019123397</v>
       </c>
       <c r="Y3" t="n">
-        <v>578.2064886541781</v>
+        <v>503.1101019123397</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>816.3372531812076</v>
+        <v>501.1882819697395</v>
       </c>
       <c r="C4" t="n">
-        <v>942.3392589996434</v>
+        <v>627.1902877881753</v>
       </c>
       <c r="D4" t="n">
-        <v>1055.658403124643</v>
+        <v>627.1902877881753</v>
       </c>
       <c r="E4" t="n">
-        <v>1160.134573790939</v>
+        <v>745.0191919995883</v>
       </c>
       <c r="F4" t="n">
-        <v>1160.134573790939</v>
+        <v>869.3801645915238</v>
       </c>
       <c r="G4" t="n">
-        <v>1160.134573790939</v>
+        <v>1022.970610806278</v>
       </c>
       <c r="H4" t="n">
-        <v>1160.134573790939</v>
+        <v>1022.970610806278</v>
       </c>
       <c r="I4" t="n">
-        <v>1386.743548464727</v>
+        <v>1249.633272693181</v>
       </c>
       <c r="J4" t="n">
-        <v>1386.743548464727</v>
+        <v>1249.633272693181</v>
       </c>
       <c r="K4" t="n">
-        <v>1386.743548464727</v>
+        <v>1381.361257449721</v>
       </c>
       <c r="L4" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="M4" t="n">
-        <v>1294.017231267251</v>
+        <v>1292.946305617309</v>
       </c>
       <c r="N4" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.742122945132</v>
       </c>
       <c r="O4" t="n">
-        <v>932.9209073660642</v>
+        <v>932.3861797621563</v>
       </c>
       <c r="P4" t="n">
-        <v>665.0402361121327</v>
+        <v>664.7258098826245</v>
       </c>
       <c r="Q4" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3053387456568</v>
       </c>
       <c r="R4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="S4" t="n">
-        <v>70.34367574991084</v>
+        <v>70.29478771712391</v>
       </c>
       <c r="T4" t="n">
-        <v>259.1973975316665</v>
+        <v>70.29478771712391</v>
       </c>
       <c r="U4" t="n">
-        <v>505.7585226289696</v>
+        <v>238.4001532792538</v>
       </c>
       <c r="V4" t="n">
-        <v>704.5799155149155</v>
+        <v>238.4001532792538</v>
       </c>
       <c r="W4" t="n">
-        <v>704.5799155149155</v>
+        <v>238.4001532792538</v>
       </c>
       <c r="X4" t="n">
-        <v>704.5799155149155</v>
+        <v>389.4309443034473</v>
       </c>
       <c r="Y4" t="n">
-        <v>704.5799155149155</v>
+        <v>389.4309443034473</v>
       </c>
     </row>
     <row r="5">
@@ -4534,49 +4534,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.731003807232</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C5" t="n">
-        <v>58.7566823496624</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D5" t="n">
-        <v>48.31309069324847</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E5" t="n">
-        <v>43.90572745398721</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F5" t="n">
-        <v>38.96670855700554</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G5" t="n">
-        <v>35.58557518755106</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H5" t="n">
-        <v>31.736856432148</v>
+        <v>29.92</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>400.18</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K5" t="n">
-        <v>633.3261931588676</v>
+        <v>400.2796902997726</v>
       </c>
       <c r="L5" t="n">
-        <v>697.388108133742</v>
+        <v>464.9696632645968</v>
       </c>
       <c r="M5" t="n">
-        <v>1067.648108133742</v>
+        <v>835.2296632645968</v>
       </c>
       <c r="N5" t="n">
-        <v>1437.908108133742</v>
+        <v>835.2296632645968</v>
       </c>
       <c r="O5" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P5" t="n">
-        <v>1496</v>
+        <v>1125.74</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4585,25 +4585,25 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1409.632174038565</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T5" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U5" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V5" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W5" t="n">
-        <v>498.2245180486953</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X5" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y5" t="n">
-        <v>191.5585926512467</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1075.987801776748</v>
+        <v>709.4154597606574</v>
       </c>
       <c r="C6" t="n">
-        <v>1075.987801776748</v>
+        <v>709.4154597606574</v>
       </c>
       <c r="D6" t="n">
-        <v>1075.987801776748</v>
+        <v>709.4154597606574</v>
       </c>
       <c r="E6" t="n">
-        <v>729.8543702394629</v>
+        <v>363.2820282233719</v>
       </c>
       <c r="F6" t="n">
-        <v>386.787458787062</v>
+        <v>363.2820282233719</v>
       </c>
       <c r="G6" t="n">
-        <v>386.787458787062</v>
+        <v>363.2820282233719</v>
       </c>
       <c r="H6" t="n">
-        <v>53.40444714459358</v>
+        <v>29.92</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
       </c>
       <c r="J6" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K6" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L6" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M6" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N6" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P6" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1346.247111942856</v>
+        <v>1357.070632947731</v>
       </c>
       <c r="R6" t="n">
-        <v>1211.245105910912</v>
+        <v>1222.20352304691</v>
       </c>
       <c r="S6" t="n">
-        <v>1148.125094511552</v>
+        <v>1159.12386804168</v>
       </c>
       <c r="T6" t="n">
-        <v>1143.60646374105</v>
+        <v>1154.613994656351</v>
       </c>
       <c r="U6" t="n">
-        <v>1143.408558894664</v>
+        <v>776.8362168785728</v>
       </c>
       <c r="V6" t="n">
-        <v>1128.75131930727</v>
+        <v>762.1789772911787</v>
       </c>
       <c r="W6" t="n">
-        <v>1096.051174953908</v>
+        <v>729.4788329378166</v>
       </c>
       <c r="X6" t="n">
-        <v>1075.987801776748</v>
+        <v>709.4154597606574</v>
       </c>
       <c r="Y6" t="n">
-        <v>1075.987801776748</v>
+        <v>709.4154597606574</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>259.1973975316665</v>
+        <v>630.9281493480643</v>
       </c>
       <c r="C7" t="n">
-        <v>344.620323690067</v>
+        <v>630.9281493480643</v>
       </c>
       <c r="D7" t="n">
-        <v>457.9394678150671</v>
+        <v>630.9281493480643</v>
       </c>
       <c r="E7" t="n">
-        <v>575.7683720264802</v>
+        <v>630.9281493480643</v>
       </c>
       <c r="F7" t="n">
-        <v>700.1293446184156</v>
+        <v>630.9281493480643</v>
       </c>
       <c r="G7" t="n">
-        <v>853.7180055872682</v>
+        <v>784.5185955628184</v>
       </c>
       <c r="H7" t="n">
-        <v>1024.853581566338</v>
+        <v>784.5185955628184</v>
       </c>
       <c r="I7" t="n">
-        <v>1251.462556240126</v>
+        <v>1011.181257449721</v>
       </c>
       <c r="J7" t="n">
-        <v>1251.462556240126</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="K7" t="n">
-        <v>1382.983127881912</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M7" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N7" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O7" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P7" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R7" t="n">
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.34367574991084</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T7" t="n">
-        <v>259.1973975316665</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="U7" t="n">
-        <v>259.1973975316665</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="V7" t="n">
-        <v>259.1973975316665</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="W7" t="n">
-        <v>259.1973975316665</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="X7" t="n">
-        <v>259.1973975316665</v>
+        <v>410.2669283919256</v>
       </c>
       <c r="Y7" t="n">
-        <v>259.1973975316665</v>
+        <v>519.1708116817722</v>
       </c>
     </row>
     <row r="8">
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.731003807232</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C8" t="n">
-        <v>58.7566823496624</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D8" t="n">
-        <v>48.31309069324847</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E8" t="n">
-        <v>43.90572745398721</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F8" t="n">
-        <v>38.96670855700554</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G8" t="n">
-        <v>35.58557518755106</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H8" t="n">
-        <v>31.736856432148</v>
+        <v>29.92</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
@@ -4798,19 +4798,19 @@
         <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>451.8183303517587</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>515.8802453266331</v>
+        <v>835.1299729648241</v>
       </c>
       <c r="M8" t="n">
-        <v>697.388108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="N8" t="n">
-        <v>1067.648108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O8" t="n">
-        <v>1067.648108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P8" t="n">
         <v>1125.74</v>
@@ -4822,25 +4822,25 @@
         <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T8" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U8" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V8" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W8" t="n">
-        <v>498.2245180486953</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X8" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.5585926512467</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="9">
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1056.313862392149</v>
+        <v>862.6043898612918</v>
       </c>
       <c r="C9" t="n">
-        <v>1056.313862392149</v>
+        <v>862.6043898612918</v>
       </c>
       <c r="D9" t="n">
-        <v>704.8616534045707</v>
+        <v>862.6043898612918</v>
       </c>
       <c r="E9" t="n">
-        <v>358.7282218672851</v>
+        <v>706.3489396757728</v>
       </c>
       <c r="F9" t="n">
-        <v>358.7282218672851</v>
+        <v>363.2820282233719</v>
       </c>
       <c r="G9" t="n">
-        <v>29.92</v>
+        <v>363.2820282233719</v>
       </c>
       <c r="H9" t="n">
         <v>29.92</v>
@@ -4874,52 +4874,52 @@
         <v>29.92</v>
       </c>
       <c r="J9" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K9" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L9" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M9" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N9" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P9" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1346.247111942856</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1191.571166526312</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S9" t="n">
-        <v>1128.451155126953</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T9" t="n">
-        <v>1123.932524356451</v>
+        <v>1293.343447077155</v>
       </c>
       <c r="U9" t="n">
-        <v>1123.734619510064</v>
+        <v>1293.145685169591</v>
       </c>
       <c r="V9" t="n">
-        <v>1109.07737992267</v>
+        <v>915.3679073918131</v>
       </c>
       <c r="W9" t="n">
-        <v>1076.377235569308</v>
+        <v>882.667763038451</v>
       </c>
       <c r="X9" t="n">
-        <v>1056.313862392149</v>
+        <v>862.6043898612918</v>
       </c>
       <c r="Y9" t="n">
-        <v>1056.313862392149</v>
+        <v>862.6043898612918</v>
       </c>
     </row>
     <row r="10">
@@ -4929,52 +4929,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1210.2445873942</v>
+        <v>728.1307008154461</v>
       </c>
       <c r="C10" t="n">
-        <v>1210.2445873942</v>
+        <v>728.1307008154461</v>
       </c>
       <c r="D10" t="n">
-        <v>1210.2445873942</v>
+        <v>841.4498449404462</v>
       </c>
       <c r="E10" t="n">
-        <v>1210.2445873942</v>
+        <v>841.4498449404462</v>
       </c>
       <c r="F10" t="n">
-        <v>1334.605559986135</v>
+        <v>883.4791106530447</v>
       </c>
       <c r="G10" t="n">
-        <v>1382.983127881912</v>
+        <v>883.4791106530447</v>
       </c>
       <c r="H10" t="n">
-        <v>1382.983127881912</v>
+        <v>883.4791106530447</v>
       </c>
       <c r="I10" t="n">
-        <v>1382.983127881912</v>
+        <v>883.4791106530447</v>
       </c>
       <c r="J10" t="n">
-        <v>1382.983127881912</v>
+        <v>1253.739110653045</v>
       </c>
       <c r="K10" t="n">
-        <v>1382.983127881912</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L10" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M10" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N10" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O10" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P10" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q10" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R10" t="n">
         <v>29.92</v>
@@ -4983,22 +4983,22 @@
         <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>218.7737217817557</v>
+        <v>218.7813496506081</v>
       </c>
       <c r="U10" t="n">
-        <v>465.3348468790587</v>
+        <v>465.3425721249604</v>
       </c>
       <c r="V10" t="n">
-        <v>664.1562397650047</v>
+        <v>465.3425721249604</v>
       </c>
       <c r="W10" t="n">
-        <v>836.0471580246821</v>
+        <v>465.3425721249604</v>
       </c>
       <c r="X10" t="n">
-        <v>987.0779490488756</v>
+        <v>616.3733631491539</v>
       </c>
       <c r="Y10" t="n">
-        <v>1098.487249727908</v>
+        <v>616.3733631491539</v>
       </c>
     </row>
     <row r="11">
@@ -5032,22 +5032,22 @@
         <v>51.92</v>
       </c>
       <c r="J11" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K11" t="n">
-        <v>1201.938527309012</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L11" t="n">
-        <v>1844.448527309012</v>
+        <v>950.0896384907273</v>
       </c>
       <c r="M11" t="n">
-        <v>2238.277892278425</v>
+        <v>1592.599638490728</v>
       </c>
       <c r="N11" t="n">
-        <v>2238.277892278425</v>
+        <v>2235.109638490728</v>
       </c>
       <c r="O11" t="n">
-        <v>2399.40799366138</v>
+        <v>2396.239739873683</v>
       </c>
       <c r="P11" t="n">
         <v>2596</v>
@@ -5056,13 +5056,13 @@
         <v>2596</v>
       </c>
       <c r="R11" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S11" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T11" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U11" t="n">
         <v>1858.092802114017</v>
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>168.4528527561725</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C12" t="n">
-        <v>127.9478906899915</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D12" t="n">
         <v>100.7381059448373</v>
@@ -5141,22 +5141,22 @@
         <v>1753.535205884734</v>
       </c>
       <c r="T12" t="n">
-        <v>1347.095458285568</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U12" t="n">
-        <v>1267.13416483617</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V12" t="n">
-        <v>1172.678945450796</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W12" t="n">
-        <v>1060.180821299454</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X12" t="n">
-        <v>636.0770440818908</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y12" t="n">
-        <v>232.6513948231691</v>
+        <v>881.1362433080177</v>
       </c>
     </row>
     <row r="13">
@@ -5196,25 +5196,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L13" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M13" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N13" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O13" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P13" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q13" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R13" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S13" t="n">
         <v>51.92</v>
@@ -5245,25 +5245,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C14" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D14" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E14" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F14" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G14" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H14" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I14" t="n">
         <v>51.92</v>
@@ -5272,16 +5272,16 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K14" t="n">
-        <v>737.2059437357115</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L14" t="n">
-        <v>953.2578922784251</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M14" t="n">
-        <v>1595.767892278425</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N14" t="n">
-        <v>2238.277892278425</v>
+        <v>1756.89799366138</v>
       </c>
       <c r="O14" t="n">
         <v>2399.40799366138</v>
@@ -5296,25 +5296,25 @@
         <v>2596</v>
       </c>
       <c r="S14" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T14" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U14" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V14" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W14" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X14" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y14" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="15">
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>168.4528527561725</v>
+        <v>343.7981213238219</v>
       </c>
       <c r="C15" t="n">
-        <v>127.9478906899915</v>
+        <v>303.2931592576408</v>
       </c>
       <c r="D15" t="n">
-        <v>100.7381059448373</v>
+        <v>276.0833745124866</v>
       </c>
       <c r="E15" t="n">
-        <v>78.84709864997603</v>
+        <v>254.1923672176254</v>
       </c>
       <c r="F15" t="n">
-        <v>60.02261143999941</v>
+        <v>235.3678800076488</v>
       </c>
       <c r="G15" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H15" t="n">
         <v>51.92</v>
@@ -5378,22 +5378,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T15" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U15" t="n">
-        <v>1591.376589078594</v>
+        <v>1442.479433403819</v>
       </c>
       <c r="V15" t="n">
-        <v>1172.678945450796</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W15" t="n">
-        <v>735.9383970570298</v>
+        <v>1235.526089867103</v>
       </c>
       <c r="X15" t="n">
-        <v>311.8346198394665</v>
+        <v>811.4223126495401</v>
       </c>
       <c r="Y15" t="n">
-        <v>232.6513948231691</v>
+        <v>732.2390876332428</v>
       </c>
     </row>
     <row r="16">
@@ -5445,10 +5445,10 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P16" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q16" t="n">
-        <v>464.3167555675509</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R16" t="n">
         <v>82.79157247680381</v>
@@ -5482,22 +5482,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C17" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D17" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E17" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F17" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G17" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H17" t="n">
         <v>51.92</v>
@@ -5509,49 +5509,49 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K17" t="n">
-        <v>307.5796384907274</v>
+        <v>507.3398986170452</v>
       </c>
       <c r="L17" t="n">
-        <v>523.631587033441</v>
+        <v>1149.849898617045</v>
       </c>
       <c r="M17" t="n">
-        <v>1009.32297330616</v>
+        <v>1792.359898617045</v>
       </c>
       <c r="N17" t="n">
-        <v>1651.83297330616</v>
+        <v>1792.359898617045</v>
       </c>
       <c r="O17" t="n">
-        <v>1812.963074689115</v>
+        <v>1953.49</v>
       </c>
       <c r="P17" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q17" t="n">
         <v>2596</v>
       </c>
       <c r="R17" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S17" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T17" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U17" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V17" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W17" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X17" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="18">
@@ -5561,22 +5561,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>992.2829698086705</v>
+        <v>816.9377012410212</v>
       </c>
       <c r="C18" t="n">
-        <v>627.5355835000651</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D18" t="n">
-        <v>600.3257987549109</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E18" t="n">
-        <v>254.1923672176254</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F18" t="n">
-        <v>235.3678800076488</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G18" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H18" t="n">
         <v>51.92</v>
@@ -5609,28 +5609,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R18" t="n">
-        <v>2062.032218270268</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S18" t="n">
-        <v>1928.880474452383</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T18" t="n">
-        <v>1846.683151095641</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U18" t="n">
-        <v>1766.721857646244</v>
+        <v>1442.47943340382</v>
       </c>
       <c r="V18" t="n">
-        <v>1672.26663826087</v>
+        <v>1348.024214018446</v>
       </c>
       <c r="W18" t="n">
-        <v>1559.768514109528</v>
+        <v>1235.526089867104</v>
       </c>
       <c r="X18" t="n">
-        <v>1459.907161134389</v>
+        <v>1135.664736891965</v>
       </c>
       <c r="Y18" t="n">
-        <v>1380.723936118091</v>
+        <v>1056.481511875668</v>
       </c>
     </row>
     <row r="19">
@@ -5664,31 +5664,31 @@
         <v>1189.283805434826</v>
       </c>
       <c r="J19" t="n">
-        <v>1515.57615461187</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K19" t="n">
-        <v>1619.080700024148</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L19" t="n">
-        <v>1608.654647405759</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M19" t="n">
-        <v>1505.227982468592</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N19" t="n">
-        <v>1348.401726605489</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O19" t="n">
-        <v>1114.2956261117</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P19" t="n">
-        <v>819.9299076645243</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.4700425881626</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R19" t="n">
-        <v>81.94485949741562</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S19" t="n">
         <v>51.92</v>
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C20" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D20" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E20" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F20" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G20" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H20" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I20" t="n">
         <v>51.92</v>
       </c>
       <c r="J20" t="n">
-        <v>559.4285273090126</v>
+        <v>136.595091876415</v>
       </c>
       <c r="K20" t="n">
-        <v>733.5813277110226</v>
+        <v>310.7478922784251</v>
       </c>
       <c r="L20" t="n">
-        <v>949.6332762537361</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M20" t="n">
-        <v>1009.32297330616</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N20" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O20" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P20" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q20" t="n">
         <v>2596</v>
       </c>
       <c r="R20" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S20" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T20" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U20" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V20" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W20" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X20" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="21">
@@ -5798,16 +5798,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1316.525394051095</v>
+        <v>668.0405455662462</v>
       </c>
       <c r="C21" t="n">
-        <v>951.7780077424893</v>
+        <v>627.5355835000652</v>
       </c>
       <c r="D21" t="n">
-        <v>600.3257987549109</v>
+        <v>600.325798754911</v>
       </c>
       <c r="E21" t="n">
-        <v>254.1923672176254</v>
+        <v>254.1923672176255</v>
       </c>
       <c r="F21" t="n">
         <v>60.0226114399994</v>
@@ -5849,25 +5849,25 @@
         <v>2062.032218270268</v>
       </c>
       <c r="S21" t="n">
-        <v>1928.880474452383</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T21" t="n">
-        <v>1846.683151095641</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U21" t="n">
-        <v>1766.721857646244</v>
+        <v>1442.479433403819</v>
       </c>
       <c r="V21" t="n">
-        <v>1672.26663826087</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W21" t="n">
-        <v>1559.768514109528</v>
+        <v>1235.526089867103</v>
       </c>
       <c r="X21" t="n">
-        <v>1459.907161134389</v>
+        <v>1135.664736891964</v>
       </c>
       <c r="Y21" t="n">
-        <v>1380.723936118091</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="22">
@@ -5907,22 +5907,22 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L22" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M22" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N22" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O22" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P22" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q22" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R22" t="n">
         <v>82.79157247680381</v>
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C23" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D23" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E23" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F23" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G23" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H23" t="n">
         <v>51.92</v>
@@ -5995,37 +5995,37 @@
         <v>2235.109638490728</v>
       </c>
       <c r="O23" t="n">
-        <v>2396.239739873683</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P23" t="n">
-        <v>2592.831746212303</v>
+        <v>2596</v>
       </c>
       <c r="Q23" t="n">
         <v>2596</v>
       </c>
       <c r="R23" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S23" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T23" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U23" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V23" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W23" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X23" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="24">
@@ -6035,25 +6035,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>168.4528527561725</v>
+        <v>992.2829698086706</v>
       </c>
       <c r="C24" t="n">
-        <v>127.9478906899915</v>
+        <v>951.7780077424895</v>
       </c>
       <c r="D24" t="n">
-        <v>100.7381059448373</v>
+        <v>924.5682229973354</v>
       </c>
       <c r="E24" t="n">
-        <v>78.84709864997603</v>
+        <v>902.6772157024742</v>
       </c>
       <c r="F24" t="n">
-        <v>60.02261143999941</v>
+        <v>559.6103042500733</v>
       </c>
       <c r="G24" t="n">
-        <v>55.98259997866057</v>
+        <v>249.5693819920296</v>
       </c>
       <c r="H24" t="n">
-        <v>51.92</v>
+        <v>245.506782013369</v>
       </c>
       <c r="I24" t="n">
         <v>51.92</v>
@@ -6083,28 +6083,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R24" t="n">
-        <v>1737.789794027844</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S24" t="n">
-        <v>1280.395625967535</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T24" t="n">
-        <v>873.9558783683688</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U24" t="n">
-        <v>618.6493163513212</v>
+        <v>1442.479433403819</v>
       </c>
       <c r="V24" t="n">
-        <v>524.1940969659473</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W24" t="n">
-        <v>411.6959728146054</v>
+        <v>1235.526089867103</v>
       </c>
       <c r="X24" t="n">
-        <v>311.8346198394665</v>
+        <v>1135.664736891964</v>
       </c>
       <c r="Y24" t="n">
-        <v>232.6513948231691</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="25">
@@ -6129,40 +6129,40 @@
         <v>855.3151236491811</v>
       </c>
       <c r="G25" t="n">
-        <v>931.1258141262372</v>
+        <v>931.1258141262304</v>
       </c>
       <c r="H25" t="n">
-        <v>1027.892525187274</v>
+        <v>1027.892525187267</v>
       </c>
       <c r="I25" t="n">
-        <v>1189.283805434832</v>
+        <v>1189.283805434826</v>
       </c>
       <c r="J25" t="n">
-        <v>1515.576154611874</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K25" t="n">
-        <v>1619.080700024152</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L25" t="n">
-        <v>1608.654647405763</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M25" t="n">
-        <v>1505.227982468595</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N25" t="n">
-        <v>1348.401726605493</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O25" t="n">
-        <v>1114.295626111704</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P25" t="n">
-        <v>819.9299076645281</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.4700425881665</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R25" t="n">
-        <v>81.94485949741937</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S25" t="n">
         <v>51.92</v>
@@ -6205,7 +6205,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F26" t="n">
-        <v>207.6991338872046</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G26" t="n">
         <v>125.5027119537179</v>
@@ -6217,31 +6217,31 @@
         <v>51.92</v>
       </c>
       <c r="J26" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K26" t="n">
-        <v>307.5796384907274</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L26" t="n">
-        <v>523.631587033441</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M26" t="n">
-        <v>563.4049796447796</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N26" t="n">
-        <v>1205.91497964478</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="O26" t="n">
-        <v>1367.045081027735</v>
+        <v>2234.653276253736</v>
       </c>
       <c r="P26" t="n">
-        <v>2009.555081027735</v>
+        <v>2431.245282592356</v>
       </c>
       <c r="Q26" t="n">
         <v>2596</v>
       </c>
       <c r="R26" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S26" t="n">
         <v>2451.762030971221</v>
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1316.525394051095</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C27" t="n">
-        <v>951.7780077424895</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D27" t="n">
-        <v>600.3257987549111</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E27" t="n">
-        <v>578.43479146005</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F27" t="n">
         <v>384.2650356824237</v>
       </c>
       <c r="G27" t="n">
-        <v>55.98259997866057</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H27" t="n">
         <v>51.92</v>
@@ -6323,25 +6323,25 @@
         <v>2062.032218270268</v>
       </c>
       <c r="S27" t="n">
-        <v>1928.880474452383</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T27" t="n">
-        <v>1846.683151095642</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U27" t="n">
-        <v>1766.721857646244</v>
+        <v>1118.237009161395</v>
       </c>
       <c r="V27" t="n">
-        <v>1672.26663826087</v>
+        <v>1023.781789776021</v>
       </c>
       <c r="W27" t="n">
-        <v>1559.768514109528</v>
+        <v>911.2836656246792</v>
       </c>
       <c r="X27" t="n">
-        <v>1459.907161134389</v>
+        <v>811.4223126495402</v>
       </c>
       <c r="Y27" t="n">
-        <v>1380.723936118092</v>
+        <v>556.8938190655934</v>
       </c>
     </row>
     <row r="28">
@@ -6381,22 +6381,22 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L28" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M28" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N28" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O28" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P28" t="n">
         <v>820.7766206439126</v>
       </c>
       <c r="Q28" t="n">
-        <v>464.3167555675509</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R28" t="n">
         <v>82.79157247680381</v>
@@ -6448,22 +6448,22 @@
         <v>125.9679517166617</v>
       </c>
       <c r="H29" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I29" t="n">
         <v>51.92</v>
       </c>
       <c r="J29" t="n">
-        <v>133.4268380887174</v>
+        <v>192.6601729041496</v>
       </c>
       <c r="K29" t="n">
-        <v>307.5796384907274</v>
+        <v>366.8129733061596</v>
       </c>
       <c r="L29" t="n">
-        <v>523.631587033441</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="M29" t="n">
-        <v>1009.32297330616</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N29" t="n">
         <v>1651.83297330616</v>
@@ -6509,16 +6509,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>168.4528527561725</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C30" t="n">
-        <v>127.9478906899915</v>
+        <v>452.1903149324158</v>
       </c>
       <c r="D30" t="n">
-        <v>100.7381059448373</v>
+        <v>424.9805301872616</v>
       </c>
       <c r="E30" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F30" t="n">
         <v>60.0226114399994</v>
@@ -6566,19 +6566,19 @@
         <v>1846.683151095641</v>
       </c>
       <c r="U30" t="n">
-        <v>1591.376589078594</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V30" t="n">
-        <v>1172.678945450796</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W30" t="n">
-        <v>735.9383970570298</v>
+        <v>1235.526089867103</v>
       </c>
       <c r="X30" t="n">
-        <v>311.8346198394665</v>
+        <v>960.3194683243152</v>
       </c>
       <c r="Y30" t="n">
-        <v>232.6513948231691</v>
+        <v>881.1362433080178</v>
       </c>
     </row>
     <row r="31">
@@ -6618,25 +6618,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L31" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M31" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N31" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O31" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P31" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q31" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R31" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S31" t="n">
         <v>51.92</v>
@@ -6691,25 +6691,25 @@
         <v>51.92</v>
       </c>
       <c r="J32" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K32" t="n">
-        <v>307.5796384907274</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L32" t="n">
-        <v>523.631587033441</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M32" t="n">
-        <v>1166.141587033441</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N32" t="n">
-        <v>1808.651587033441</v>
+        <v>2234.653276253736</v>
       </c>
       <c r="O32" t="n">
-        <v>1969.781688416396</v>
+        <v>2395.783377636692</v>
       </c>
       <c r="P32" t="n">
-        <v>2166.373694755016</v>
+        <v>2596</v>
       </c>
       <c r="Q32" t="n">
         <v>2596</v>
@@ -6724,7 +6724,7 @@
         <v>2189.982954384821</v>
       </c>
       <c r="U32" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V32" t="n">
         <v>1546.122070632377</v>
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1316.525394051095</v>
+        <v>1010.52448325439</v>
       </c>
       <c r="C33" t="n">
-        <v>1276.020431984914</v>
+        <v>970.019521188209</v>
       </c>
       <c r="D33" t="n">
-        <v>1248.81064723976</v>
+        <v>618.5673122006306</v>
       </c>
       <c r="E33" t="n">
-        <v>1226.919639944898</v>
+        <v>596.6763049057694</v>
       </c>
       <c r="F33" t="n">
-        <v>883.8527284924974</v>
+        <v>577.8518176957928</v>
       </c>
       <c r="G33" t="n">
-        <v>573.8118062344539</v>
+        <v>249.5693819920296</v>
       </c>
       <c r="H33" t="n">
         <v>245.506782013369</v>
@@ -6800,22 +6800,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T33" t="n">
-        <v>1846.683151095642</v>
+        <v>1540.682240298936</v>
       </c>
       <c r="U33" t="n">
-        <v>1766.721857646244</v>
+        <v>1460.720946849539</v>
       </c>
       <c r="V33" t="n">
-        <v>1672.26663826087</v>
+        <v>1366.265727464165</v>
       </c>
       <c r="W33" t="n">
-        <v>1559.768514109528</v>
+        <v>1253.767603312823</v>
       </c>
       <c r="X33" t="n">
-        <v>1459.907161134389</v>
+        <v>1153.906250337684</v>
       </c>
       <c r="Y33" t="n">
-        <v>1380.723936118092</v>
+        <v>1074.723025321387</v>
       </c>
     </row>
     <row r="34">
@@ -6873,7 +6873,7 @@
         <v>463.4700425881596</v>
       </c>
       <c r="R34" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S34" t="n">
         <v>51.92</v>
@@ -6904,22 +6904,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C35" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D35" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E35" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F35" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G35" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H35" t="n">
         <v>51.92</v>
@@ -6931,49 +6931,49 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K35" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L35" t="n">
-        <v>523.631587033441</v>
+        <v>1114.38799366138</v>
       </c>
       <c r="M35" t="n">
-        <v>563.4049796447796</v>
+        <v>1756.89799366138</v>
       </c>
       <c r="N35" t="n">
-        <v>1205.91497964478</v>
+        <v>1756.89799366138</v>
       </c>
       <c r="O35" t="n">
-        <v>1367.045081027735</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P35" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q35" t="n">
         <v>2596</v>
       </c>
       <c r="R35" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S35" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T35" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U35" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V35" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W35" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X35" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y35" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="36">
@@ -6983,16 +6983,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1316.525394051095</v>
+        <v>492.6952769985968</v>
       </c>
       <c r="C36" t="n">
-        <v>1100.675163417264</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D36" t="n">
-        <v>749.2229544296858</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E36" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F36" t="n">
         <v>60.0226114399994</v>
@@ -7040,19 +7040,19 @@
         <v>1846.683151095641</v>
       </c>
       <c r="U36" t="n">
-        <v>1766.721857646244</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V36" t="n">
-        <v>1672.26663826087</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W36" t="n">
-        <v>1559.768514109528</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X36" t="n">
-        <v>1459.907161134389</v>
+        <v>960.3194683243149</v>
       </c>
       <c r="Y36" t="n">
-        <v>1380.723936118091</v>
+        <v>881.1362433080176</v>
       </c>
     </row>
     <row r="37">
@@ -7147,19 +7147,19 @@
         <v>467.3482868367445</v>
       </c>
       <c r="D38" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E38" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F38" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G38" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H38" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I38" t="n">
         <v>51.92</v>
@@ -7168,16 +7168,16 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K38" t="n">
-        <v>775.9368380887173</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L38" t="n">
-        <v>991.9887866314309</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M38" t="n">
-        <v>1634.498786631431</v>
+        <v>527.9430746891146</v>
       </c>
       <c r="N38" t="n">
-        <v>1651.83297330616</v>
+        <v>1170.453074689115</v>
       </c>
       <c r="O38" t="n">
         <v>1812.963074689115</v>
@@ -7220,19 +7220,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>492.6952769985968</v>
+        <v>992.2829698086708</v>
       </c>
       <c r="C39" t="n">
-        <v>127.9478906899915</v>
+        <v>627.5355835000655</v>
       </c>
       <c r="D39" t="n">
-        <v>100.7381059448373</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E39" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F39" t="n">
-        <v>60.02261143999941</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G39" t="n">
         <v>55.98259997866057</v>
@@ -7283,13 +7283,13 @@
         <v>1672.26663826087</v>
       </c>
       <c r="W39" t="n">
-        <v>1559.768514109528</v>
+        <v>1235.526089867104</v>
       </c>
       <c r="X39" t="n">
-        <v>1284.561892566739</v>
+        <v>1135.664736891965</v>
       </c>
       <c r="Y39" t="n">
-        <v>881.1362433080176</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="40">
@@ -7378,43 +7378,43 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>597.1205880922939</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C41" t="n">
-        <v>467.3482868367445</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D41" t="n">
-        <v>377.1067153823507</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E41" t="n">
-        <v>292.9013723451097</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F41" t="n">
-        <v>208.1643736501482</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G41" t="n">
-        <v>125.9679517166614</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H41" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I41" t="n">
         <v>51.92</v>
       </c>
       <c r="J41" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K41" t="n">
-        <v>737.2059437357115</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L41" t="n">
-        <v>953.2578922784251</v>
+        <v>1417.990475851726</v>
       </c>
       <c r="M41" t="n">
-        <v>1595.767892278425</v>
+        <v>1756.89799366138</v>
       </c>
       <c r="N41" t="n">
-        <v>2238.277892278425</v>
+        <v>1756.89799366138</v>
       </c>
       <c r="O41" t="n">
         <v>2399.40799366138</v>
@@ -7438,16 +7438,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V41" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W41" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X41" t="n">
-        <v>951.9859877270221</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y41" t="n">
-        <v>759.7461567342884</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>912.8601939406433</v>
+        <v>492.6952769985968</v>
       </c>
       <c r="C42" t="n">
-        <v>872.3552318744622</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D42" t="n">
-        <v>845.1454471293081</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E42" t="n">
-        <v>823.2544398344469</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F42" t="n">
-        <v>804.4299526244703</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G42" t="n">
-        <v>476.1475169207072</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H42" t="n">
-        <v>147.8424926996223</v>
+        <v>51.92</v>
       </c>
       <c r="I42" t="n">
         <v>51.92</v>
@@ -7502,31 +7502,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q42" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R42" t="n">
-        <v>1658.367018159816</v>
+        <v>1886.686949702618</v>
       </c>
       <c r="S42" t="n">
-        <v>1525.215274341931</v>
+        <v>1429.292781642309</v>
       </c>
       <c r="T42" t="n">
-        <v>1443.01795098519</v>
+        <v>1347.095458285568</v>
       </c>
       <c r="U42" t="n">
-        <v>1363.056657535792</v>
+        <v>1267.13416483617</v>
       </c>
       <c r="V42" t="n">
-        <v>1268.601438150418</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W42" t="n">
-        <v>1156.103313999076</v>
+        <v>735.9383970570296</v>
       </c>
       <c r="X42" t="n">
-        <v>1056.241961023937</v>
+        <v>636.0770440818907</v>
       </c>
       <c r="Y42" t="n">
-        <v>977.0587360076398</v>
+        <v>556.8938190655933</v>
       </c>
     </row>
     <row r="43">
@@ -7536,55 +7536,55 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>686.6440969024743</v>
+        <v>686.6440969023969</v>
       </c>
       <c r="C43" t="n">
-        <v>734.4361027209101</v>
+        <v>734.4361027208327</v>
       </c>
       <c r="D43" t="n">
-        <v>769.5452468459101</v>
+        <v>769.5452468458327</v>
       </c>
       <c r="E43" t="n">
-        <v>809.1641510573231</v>
+        <v>809.1641510572457</v>
       </c>
       <c r="F43" t="n">
-        <v>855.3151236492586</v>
+        <v>855.3151236491811</v>
       </c>
       <c r="G43" t="n">
-        <v>931.1258141263078</v>
+        <v>931.1258141262304</v>
       </c>
       <c r="H43" t="n">
-        <v>1027.892525187345</v>
+        <v>1027.892525187267</v>
       </c>
       <c r="I43" t="n">
-        <v>1189.283805434903</v>
+        <v>1189.283805434826</v>
       </c>
       <c r="J43" t="n">
-        <v>1515.576154611945</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K43" t="n">
-        <v>1619.080700024223</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L43" t="n">
-        <v>1608.654647405834</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M43" t="n">
-        <v>1505.227982468666</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N43" t="n">
-        <v>1348.401726605563</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O43" t="n">
-        <v>1114.295626111774</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P43" t="n">
-        <v>819.929907664599</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q43" t="n">
-        <v>463.4700425882374</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R43" t="n">
-        <v>81.94485949749031</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7596,16 +7596,16 @@
         <v>332.7843563872555</v>
       </c>
       <c r="V43" t="n">
-        <v>453.3957492732789</v>
+        <v>453.3957492732014</v>
       </c>
       <c r="W43" t="n">
-        <v>547.0766675329563</v>
+        <v>547.0766675328789</v>
       </c>
       <c r="X43" t="n">
-        <v>619.8974585571499</v>
+        <v>619.8974585570725</v>
       </c>
       <c r="Y43" t="n">
-        <v>653.0967592361822</v>
+        <v>653.0967592361047</v>
       </c>
     </row>
     <row r="44">
@@ -7615,25 +7615,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C44" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D44" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E44" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F44" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G44" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H44" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I44" t="n">
         <v>51.92</v>
@@ -7642,49 +7642,49 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K44" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L44" t="n">
-        <v>950.0896384907273</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M44" t="n">
-        <v>1592.599638490728</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N44" t="n">
-        <v>2235.109638490728</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O44" t="n">
-        <v>2396.239739873683</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P44" t="n">
-        <v>2592.831746212303</v>
+        <v>2596</v>
       </c>
       <c r="Q44" t="n">
         <v>2596</v>
       </c>
       <c r="R44" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S44" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T44" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U44" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V44" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W44" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X44" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y44" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1316.525394051095</v>
+        <v>668.0405455662465</v>
       </c>
       <c r="C45" t="n">
-        <v>1276.020431984914</v>
+        <v>627.5355835000654</v>
       </c>
       <c r="D45" t="n">
-        <v>924.5682229973352</v>
+        <v>600.3257987549113</v>
       </c>
       <c r="E45" t="n">
-        <v>902.677215702474</v>
+        <v>254.1923672176258</v>
       </c>
       <c r="F45" t="n">
-        <v>559.6103042500731</v>
+        <v>235.3678800076491</v>
       </c>
       <c r="G45" t="n">
-        <v>555.5702927887343</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H45" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I45" t="n">
         <v>51.92</v>
@@ -7748,22 +7748,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T45" t="n">
-        <v>1846.683151095641</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U45" t="n">
-        <v>1766.721857646244</v>
+        <v>1442.479433403819</v>
       </c>
       <c r="V45" t="n">
-        <v>1672.26663826087</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W45" t="n">
-        <v>1559.768514109528</v>
+        <v>1235.526089867104</v>
       </c>
       <c r="X45" t="n">
-        <v>1459.907161134389</v>
+        <v>1135.664736891965</v>
       </c>
       <c r="Y45" t="n">
-        <v>1380.723936118091</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="46">
@@ -7776,52 +7776,52 @@
         <v>686.6440969023969</v>
       </c>
       <c r="C46" t="n">
-        <v>734.436102720921</v>
+        <v>734.4361027208327</v>
       </c>
       <c r="D46" t="n">
-        <v>769.545246845921</v>
+        <v>769.5452468458327</v>
       </c>
       <c r="E46" t="n">
-        <v>809.164151057334</v>
+        <v>809.1641510572457</v>
       </c>
       <c r="F46" t="n">
-        <v>855.3151236492695</v>
+        <v>855.3151236491811</v>
       </c>
       <c r="G46" t="n">
-        <v>931.1258141263187</v>
+        <v>931.1258141262304</v>
       </c>
       <c r="H46" t="n">
-        <v>1027.892525187356</v>
+        <v>1027.892525187267</v>
       </c>
       <c r="I46" t="n">
-        <v>1189.283805434914</v>
+        <v>1189.283805434826</v>
       </c>
       <c r="J46" t="n">
-        <v>1515.576154611956</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K46" t="n">
-        <v>1619.080700024234</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L46" t="n">
-        <v>1608.654647405845</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M46" t="n">
-        <v>1505.227982468677</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N46" t="n">
-        <v>1348.401726605574</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O46" t="n">
-        <v>1114.295626111785</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P46" t="n">
-        <v>819.9299076646098</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q46" t="n">
-        <v>463.4700425882481</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R46" t="n">
-        <v>81.94485949750111</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S46" t="n">
         <v>51.92</v>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>320.3286984924623</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>846.2608914614127</v>
+        <v>844.554996989051</v>
       </c>
       <c r="N2" t="n">
-        <v>404.0826666125488</v>
+        <v>636.5937645210809</v>
       </c>
       <c r="O2" t="n">
-        <v>243.1789695182578</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P2" t="n">
-        <v>315.3213213472141</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>502.5418702571336</v>
+        <v>501.1077446289929</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8058,7 +8058,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O3" t="n">
-        <v>382.6817988009037</v>
+        <v>378.9241368124838</v>
       </c>
       <c r="P3" t="n">
         <v>219.1507118405495</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>374.2405037325275</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>183.3412755627362</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>846.2608914614127</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N5" t="n">
-        <v>778.0826666125488</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O5" t="n">
-        <v>1.159015302735668</v>
+        <v>234.6696840452354</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>128.5418702571336</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>374.2405037325275</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>655.6021670241489</v>
+        <v>705.843704712591</v>
       </c>
       <c r="N8" t="n">
-        <v>778.0826666125488</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O8" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>502.5418702571336</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,25 +8675,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>473.08808040201</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>430.7657085427136</v>
       </c>
       <c r="M11" t="n">
-        <v>699.241868512898</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N11" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.200256351209248</v>
       </c>
       <c r="Q11" t="n">
         <v>23.48346824708341</v>
@@ -8915,7 +8915,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>433.9659648939233</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -8924,10 +8924,10 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N14" t="n">
-        <v>879.4920535472222</v>
+        <v>827.2156966057469</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -9152,25 +9152,25 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>201.7780405316341</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M17" t="n">
-        <v>792.031789021288</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N17" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,16 +9386,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>3.200256351209731</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M20" t="n">
-        <v>361.7270524351312</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N20" t="n">
         <v>879.4920535472222</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9638,13 +9638,13 @@
         <v>879.4920535472222</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.200256351209561</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>26.68372459829277</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,7 +9860,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -9869,19 +9869,19 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>341.6095732017122</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N26" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P26" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>189.9023747194511</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,19 +10097,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>59.8316513287194</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M29" t="n">
-        <v>792.031789021288</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N29" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10334,7 +10334,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -10352,10 +10352,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3.661228307766294</v>
       </c>
       <c r="Q32" t="n">
-        <v>457.4494331410071</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,25 +10574,25 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>123.6355626565146</v>
       </c>
       <c r="M35" t="n">
-        <v>341.6095732017122</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N35" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P35" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,19 +10811,19 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>950.4344291498551</v>
+        <v>305.789467185889</v>
       </c>
       <c r="N38" t="n">
-        <v>248.0013330166451</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -11045,22 +11045,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>433.9659648939233</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>950.4344291498551</v>
+        <v>643.7652552202129</v>
       </c>
       <c r="N41" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -11285,13 +11285,13 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L44" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>950.4344291498551</v>
+        <v>911.3123136417682</v>
       </c>
       <c r="N44" t="n">
         <v>879.4920535472222</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>26.68372459829277</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1.927393539208538</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -23411,7 +23411,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8382458495976959</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -23432,7 +23432,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23660,10 +23660,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8382458495973992</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -23888,7 +23888,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8382458495943084</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24122,7 +24122,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -24140,7 +24140,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8382458495905887</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -24608,7 +24608,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0.8382458495973992</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -24854,7 +24854,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -25088,10 +25088,10 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>0.8382458495973424</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.8382458495203586</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26018,7 +26018,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>0.8382458495976959</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -26039,7 +26039,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.8382458495096721</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>797725.6530297217</v>
+        <v>797448.2902684262</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1521867.451220963</v>
+        <v>1521696.852918674</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2246009.249412206</v>
+        <v>2245838.651109917</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2969705.156810724</v>
+        <v>2969616.940008434</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3693835.387209242</v>
+        <v>3693747.170406953</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4417965.617607759</v>
+        <v>4417877.40080547</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5142095.848006274</v>
+        <v>5142007.631203984</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5866226.078404789</v>
+        <v>5866137.861602499</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6590356.308803303</v>
+        <v>6590268.092001013</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7314486.539201817</v>
+        <v>7314398.322399528</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8038616.769600337</v>
+        <v>8038528.552798048</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8762746.999998862</v>
+        <v>8762658.783196572</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9486877.230397385</v>
+        <v>9486789.013595095</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10211007.46079591</v>
+        <v>10210919.24399362</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10935137.69119443</v>
+        <v>10935049.47439214</v>
       </c>
     </row>
   </sheetData>
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1479768.022390799</v>
+        <v>1479587.753273077</v>
       </c>
       <c r="C2" t="n">
         <v>1479768.022390799</v>
@@ -26281,7 +26281,7 @@
         <v>1479744.383857841</v>
       </c>
       <c r="F2" t="n">
-        <v>1479744.383857841</v>
+        <v>1479744.38385784</v>
       </c>
       <c r="G2" t="n">
         <v>1479744.38385784</v>
@@ -26290,10 +26290,10 @@
         <v>1479744.38385784</v>
       </c>
       <c r="I2" t="n">
-        <v>1479744.383857841</v>
+        <v>1479744.38385784</v>
       </c>
       <c r="J2" t="n">
-        <v>1479744.383857841</v>
+        <v>1479744.38385784</v>
       </c>
       <c r="K2" t="n">
         <v>1479744.38385784</v>
@@ -26308,10 +26308,10 @@
         <v>1479744.383857841</v>
       </c>
       <c r="O2" t="n">
-        <v>1479744.383857842</v>
+        <v>1479744.38385784</v>
       </c>
       <c r="P2" t="n">
-        <v>1479744.383857842</v>
+        <v>1479744.383857841</v>
       </c>
     </row>
     <row r="3">
@@ -26321,16 +26321,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>231098</v>
+        <v>231721</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>589550</v>
+        <v>588575</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,10 +26345,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388448</v>
+        <v>388096</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577464.9346667652</v>
+        <v>570823.1065049333</v>
       </c>
       <c r="C4" t="n">
-        <v>575456.0124792766</v>
+        <v>568738.1032495913</v>
       </c>
       <c r="D4" t="n">
-        <v>573444.3650634525</v>
+        <v>566727.0147207876</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.9797961749</v>
+        <v>483475.9886658208</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779521</v>
+        <v>481789.925847598</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562992</v>
+        <v>480101.5363259449</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457893</v>
+        <v>476717.710215435</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308645</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216767</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469921.3886193651</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589554</v>
+        <v>468216.2325286012</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604944</v>
+        <v>466508.609930139</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.493408911</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26425,13 +26425,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58590.39999999999</v>
+        <v>58551.39999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="D5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="E5" t="n">
         <v>73944.549</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>612614.6877240337</v>
+        <v>618492.2467681437</v>
       </c>
       <c r="C6" t="n">
-        <v>845721.6099115227</v>
+        <v>852065.7191412081</v>
       </c>
       <c r="D6" t="n">
-        <v>847733.2573273466</v>
+        <v>854428.8076700111</v>
       </c>
       <c r="E6" t="n">
-        <v>326310.8550616658</v>
+        <v>333748.8461920201</v>
       </c>
       <c r="F6" t="n">
-        <v>917546.917879889</v>
+        <v>924009.909010242</v>
       </c>
       <c r="G6" t="n">
-        <v>919235.3074015406</v>
+        <v>925698.2985318956</v>
       </c>
       <c r="H6" t="n">
-        <v>920926.0403115036</v>
+        <v>927389.0314418573</v>
       </c>
       <c r="I6" t="n">
-        <v>922619.1335120517</v>
+        <v>929082.1246424047</v>
       </c>
       <c r="J6" t="n">
-        <v>535866.6041269762</v>
+        <v>542681.5952573295</v>
       </c>
       <c r="K6" t="n">
-        <v>926012.4695058092</v>
+        <v>932123.460636163</v>
       </c>
       <c r="L6" t="n">
-        <v>927712.7472281539</v>
+        <v>934175.7383585079</v>
       </c>
       <c r="M6" t="n">
-        <v>832615.4551081209</v>
+        <v>839078.4462384745</v>
       </c>
       <c r="N6" t="n">
-        <v>931120.6111988857</v>
+        <v>937583.6023292397</v>
       </c>
       <c r="O6" t="n">
-        <v>676028.233797348</v>
+        <v>682491.2249277005</v>
       </c>
       <c r="P6" t="n">
-        <v>934538.341448931</v>
+        <v>941001.332579285</v>
       </c>
     </row>
   </sheetData>
@@ -26807,13 +26807,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E3" t="n">
         <v>344</v>
@@ -26859,7 +26859,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" t="n">
         <v>374</v>
@@ -26984,7 +26984,7 @@
         <v>321</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -27002,19 +27002,19 @@
         <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>-0</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
       <c r="O2" t="n">
         <v>321</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27033,7 +27033,7 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -27076,10 +27076,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>-0</v>
@@ -27100,10 +27100,10 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
@@ -27317,10 +27317,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>134.2726973711268</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>223.3220918649904</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27512,13 +27512,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>263.956842650813</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
@@ -27527,13 +27527,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27566,19 +27566,19 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>277.818744275583</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>26.1959257979226</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>400</v>
+        <v>41.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>400</v>
+        <v>46.86273944538755</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27597,31 +27597,31 @@
         <v>400</v>
       </c>
       <c r="D4" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E4" t="n">
         <v>400</v>
       </c>
-      <c r="E4" t="n">
-        <v>386.5123903584674</v>
-      </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>227.1357818393235</v>
+        <v>227.1197490524383</v>
       </c>
       <c r="I4" t="n">
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>22.26478490148153</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K4" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27645,19 +27645,19 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>320.751659684624</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>132.4740095033003</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,13 +27718,13 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
       </c>
       <c r="T5" t="n">
-        <v>400</v>
+        <v>398.0465935392084</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
@@ -27761,16 +27761,16 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>186.3230096332952</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>7.456805307090832</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27806,7 +27806,7 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>400</v>
+        <v>26.19578428848864</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27828,34 +27828,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>359.011030646429</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
         <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>227.1197490524383</v>
       </c>
       <c r="I7" t="n">
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>22.26478490148153</v>
+        <v>396.1372930982029</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27885,7 +27885,7 @@
         <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9483584875727</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
@@ -27894,10 +27894,10 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>397.4692753644589</v>
       </c>
     </row>
     <row r="8">
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>132.4740095033003</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,10 +27955,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>398.0465935392085</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27992,22 +27992,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>187.9792015382489</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,10 +28031,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
-        <v>380.5228000092467</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
@@ -28046,7 +28046,7 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>400</v>
+        <v>40.51066719152016</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
@@ -28071,31 +28071,31 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
+        <v>316.8366597178415</v>
+      </c>
+      <c r="G10" t="n">
+        <v>244.858135136612</v>
+      </c>
+      <c r="H10" t="n">
+        <v>227.1197490524383</v>
+      </c>
+      <c r="I10" t="n">
+        <v>171.047816275856</v>
+      </c>
+      <c r="J10" t="n">
+        <v>396.1372930982029</v>
+      </c>
+      <c r="K10" t="n">
         <v>400</v>
       </c>
-      <c r="G10" t="n">
-        <v>293.7261686130546</v>
-      </c>
-      <c r="H10" t="n">
-        <v>227.1357818393235</v>
-      </c>
-      <c r="I10" t="n">
-        <v>171.1020457840527</v>
-      </c>
-      <c r="J10" t="n">
-        <v>22.26478490148153</v>
-      </c>
-      <c r="K10" t="n">
-        <v>267.1509377355693</v>
-      </c>
       <c r="L10" t="n">
-        <v>400</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,7 +28116,7 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>359.1680042930194</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T10" t="n">
         <v>400</v>
@@ -28125,16 +28125,16 @@
         <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28192,7 +28192,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S11" t="n">
         <v>321</v>
@@ -28201,7 +28201,7 @@
         <v>321</v>
       </c>
       <c r="U11" t="n">
-        <v>320.5394126346857</v>
+        <v>321</v>
       </c>
       <c r="V11" t="n">
         <v>321</v>
@@ -28223,13 +28223,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>321</v>
       </c>
       <c r="D12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>321</v>
@@ -28277,7 +28277,7 @@
         <v>147.4081841180271</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U12" t="n">
         <v>321</v>
@@ -28289,7 +28289,7 @@
         <v>321</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -28402,7 +28402,7 @@
         <v>321</v>
       </c>
       <c r="I14" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28432,7 +28432,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S14" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T14" t="n">
         <v>321</v>
@@ -28460,7 +28460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>321</v>
@@ -28475,7 +28475,7 @@
         <v>321</v>
       </c>
       <c r="G15" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="H15" t="n">
         <v>321</v>
@@ -28517,13 +28517,13 @@
         <v>321</v>
       </c>
       <c r="U15" t="n">
-        <v>147.4081841180269</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -28636,7 +28636,7 @@
         <v>321</v>
       </c>
       <c r="H17" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I17" t="n">
         <v>96.76634561233286</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S17" t="n">
         <v>321</v>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>147.4081841180266</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -28712,7 +28712,7 @@
         <v>321</v>
       </c>
       <c r="G18" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="H18" t="n">
         <v>321</v>
@@ -28745,7 +28745,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>321</v>
@@ -28800,7 +28800,7 @@
         <v>321</v>
       </c>
       <c r="J19" t="n">
-        <v>321.0000000000032</v>
+        <v>321</v>
       </c>
       <c r="K19" t="n">
         <v>321</v>
@@ -28876,7 +28876,7 @@
         <v>321</v>
       </c>
       <c r="I20" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S20" t="n">
         <v>321</v>
@@ -28934,19 +28934,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>147.4081841180271</v>
+        <v>147.408184118027</v>
       </c>
       <c r="G21" t="n">
         <v>321</v>
@@ -28985,7 +28985,7 @@
         <v>321</v>
       </c>
       <c r="S21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>321</v>
@@ -29110,7 +29110,7 @@
         <v>321</v>
       </c>
       <c r="H23" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I23" t="n">
         <v>96.76634561233286</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S23" t="n">
         <v>321</v>
@@ -29183,16 +29183,16 @@
         <v>321</v>
       </c>
       <c r="F24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>321</v>
+        <v>18.05909831126218</v>
       </c>
       <c r="H24" t="n">
         <v>321</v>
       </c>
       <c r="I24" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -29219,16 +29219,16 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U24" t="n">
-        <v>147.4081841180266</v>
+        <v>321</v>
       </c>
       <c r="V24" t="n">
         <v>321</v>
@@ -29265,7 +29265,7 @@
         <v>321</v>
       </c>
       <c r="G25" t="n">
-        <v>321.0000000000069</v>
+        <v>321</v>
       </c>
       <c r="H25" t="n">
         <v>321</v>
@@ -29377,10 +29377,10 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S26" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T26" t="n">
         <v>321</v>
@@ -29411,22 +29411,22 @@
         <v>321</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E27" t="n">
         <v>321</v>
       </c>
       <c r="F27" t="n">
-        <v>147.4081841180268</v>
+        <v>321</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>191.6509141932353</v>
@@ -29459,13 +29459,13 @@
         <v>321</v>
       </c>
       <c r="S27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
         <v>321</v>
       </c>
       <c r="U27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>321</v>
@@ -29477,7 +29477,7 @@
         <v>321</v>
       </c>
       <c r="Y27" t="n">
-        <v>321</v>
+        <v>147.408184118027</v>
       </c>
     </row>
     <row r="28">
@@ -29584,10 +29584,10 @@
         <v>321</v>
       </c>
       <c r="H29" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="I29" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29645,7 +29645,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>321</v>
@@ -29657,7 +29657,7 @@
         <v>321</v>
       </c>
       <c r="F30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>321</v>
@@ -29702,16 +29702,16 @@
         <v>321</v>
       </c>
       <c r="U30" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>147.4081841180272</v>
       </c>
       <c r="Y30" t="n">
         <v>321</v>
@@ -29860,10 +29860,10 @@
         <v>321</v>
       </c>
       <c r="U32" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="V32" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="W32" t="n">
         <v>321</v>
@@ -29888,19 +29888,19 @@
         <v>321</v>
       </c>
       <c r="D33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>321</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G33" t="n">
-        <v>18.0590983112624</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -29936,7 +29936,7 @@
         <v>321</v>
       </c>
       <c r="T33" t="n">
-        <v>321</v>
+        <v>18.05909831126195</v>
       </c>
       <c r="U33" t="n">
         <v>321</v>
@@ -30058,7 +30058,7 @@
         <v>321</v>
       </c>
       <c r="H35" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="I35" t="n">
         <v>96.76634561233286</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S35" t="n">
         <v>321</v>
@@ -30119,19 +30119,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>147.4081841180271</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G36" t="n">
         <v>321</v>
@@ -30176,13 +30176,13 @@
         <v>321</v>
       </c>
       <c r="U36" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="V36" t="n">
         <v>321</v>
       </c>
       <c r="W36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>321</v>
@@ -30283,7 +30283,7 @@
         <v>321</v>
       </c>
       <c r="D38" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="E38" t="n">
         <v>321</v>
@@ -30298,7 +30298,7 @@
         <v>321</v>
       </c>
       <c r="I38" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30356,13 +30356,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>321</v>
+        <v>147.4081841180267</v>
       </c>
       <c r="E39" t="n">
         <v>321</v>
@@ -30371,7 +30371,7 @@
         <v>321</v>
       </c>
       <c r="G39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>321</v>
@@ -30419,13 +30419,13 @@
         <v>321</v>
       </c>
       <c r="W39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>147.4081841180267</v>
+        <v>321</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="40">
@@ -30532,10 +30532,10 @@
         <v>321</v>
       </c>
       <c r="H41" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I41" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30596,7 +30596,7 @@
         <v>321</v>
       </c>
       <c r="C42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>321</v>
@@ -30608,13 +30608,13 @@
         <v>321</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I42" t="n">
-        <v>96.68764642060924</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30638,13 +30638,13 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>147.408184118027</v>
       </c>
       <c r="S42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>321</v>
@@ -30656,7 +30656,7 @@
         <v>321</v>
       </c>
       <c r="W42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>321</v>
@@ -30732,7 +30732,7 @@
         <v>321</v>
       </c>
       <c r="V43" t="n">
-        <v>321.0000000000783</v>
+        <v>321</v>
       </c>
       <c r="W43" t="n">
         <v>321</v>
@@ -30772,7 +30772,7 @@
         <v>321</v>
       </c>
       <c r="I44" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S44" t="n">
         <v>321</v>
@@ -30830,28 +30830,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>321</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G45" t="n">
-        <v>321</v>
+        <v>147.4081841180268</v>
       </c>
       <c r="H45" t="n">
-        <v>18.0590983112624</v>
+        <v>321</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30887,7 +30887,7 @@
         <v>321</v>
       </c>
       <c r="U45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>321</v>
@@ -30912,7 +30912,7 @@
         <v>321</v>
       </c>
       <c r="C46" t="n">
-        <v>321.0000000000892</v>
+        <v>321</v>
       </c>
       <c r="D46" t="n">
         <v>321</v>
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H2" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I2" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J2" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K2" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M2" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N2" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O2" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P2" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q2" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R2" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S2" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T2" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H3" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I3" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J3" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K3" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L3" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M3" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O3" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P3" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R3" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S3" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H4" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I4" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J4" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K4" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L4" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M4" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N4" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O4" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P4" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R4" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S4" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T4" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31328,49 +31328,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H5" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I5" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J5" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K5" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M5" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N5" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O5" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P5" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R5" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S5" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T5" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31407,49 +31407,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H6" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I6" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J6" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K6" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L6" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M6" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O6" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P6" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R6" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S6" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31486,49 +31486,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H7" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I7" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J7" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K7" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L7" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M7" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N7" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O7" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P7" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R7" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S7" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T7" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31565,49 +31565,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H8" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I8" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J8" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K8" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M8" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N8" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O8" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P8" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R8" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S8" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T8" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31644,49 +31644,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H9" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I9" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J9" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K9" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L9" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M9" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O9" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P9" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R9" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S9" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31723,49 +31723,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H10" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I10" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J10" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K10" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L10" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M10" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N10" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O10" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P10" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R10" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S10" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T10" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K2" t="n">
-        <v>52.1599296482412</v>
+        <v>373</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512562</v>
+        <v>65.34340703517591</v>
       </c>
       <c r="M2" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>233.2284144914466</v>
       </c>
       <c r="O2" t="n">
-        <v>242.0199542155221</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>374</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q2" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K3" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L3" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M3" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O3" t="n">
-        <v>293.6569652989728</v>
+        <v>290.4110674614963</v>
       </c>
       <c r="P3" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34883,31 +34883,31 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>105.5314855215108</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>228.8979542159473</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,22 +34928,22 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>40.83199570698065</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T4" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0516415124273</v>
+        <v>169.803399557707</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0.1006972724976123</v>
+      </c>
+      <c r="K5" t="n">
         <v>374</v>
       </c>
-      <c r="K5" t="n">
-        <v>235.5012052109774</v>
-      </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517591</v>
       </c>
       <c r="M5" t="n">
         <v>374</v>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>234.1880104510425</v>
+      </c>
+      <c r="P5" t="n">
+        <v>59.25677413017286</v>
+      </c>
+      <c r="Q5" t="n">
         <v>374</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>58.67867865278593</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35059,25 +35059,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K6" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L6" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M6" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O6" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P6" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35114,37 +35114,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>86.28578399838436</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>155.1400615846995</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H7" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>228.8979542159473</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K7" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3.798404629106074</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,10 +35165,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.83199570698065</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T7" t="n">
-        <v>190.7613351330866</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -35180,10 +35180,10 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>110.0039225149966</v>
       </c>
     </row>
     <row r="8">
@@ -35220,22 +35220,22 @@
         <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>52.15992964824119</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517591</v>
       </c>
       <c r="M8" t="n">
-        <v>183.3412755627362</v>
+        <v>234.2887077235401</v>
       </c>
       <c r="N8" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
         <v>374</v>
@@ -35296,25 +35296,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K9" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L9" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M9" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O9" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P9" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35357,16 +35357,16 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>42.45380375009954</v>
       </c>
       <c r="G10" t="n">
-        <v>48.86623019775411</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -35375,13 +35375,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L10" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35405,22 +35405,22 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7613351330866</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0516415124273</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,25 +35454,25 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K11" t="n">
-        <v>648.9999999999999</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L11" t="n">
         <v>649</v>
       </c>
       <c r="M11" t="n">
-        <v>397.807439363043</v>
+        <v>649</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O11" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P11" t="n">
-        <v>198.5777841804241</v>
+        <v>201.7780405316333</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35694,7 +35694,7 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K14" t="n">
-        <v>609.8778844919133</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L14" t="n">
         <v>218.2342914572864</v>
@@ -35703,10 +35703,10 @@
         <v>649</v>
       </c>
       <c r="N14" t="n">
+        <v>596.7236430585247</v>
+      </c>
+      <c r="O14" t="n">
         <v>649</v>
-      </c>
-      <c r="O14" t="n">
-        <v>162.757678164601</v>
       </c>
       <c r="P14" t="n">
         <v>198.5777841804241</v>
@@ -35843,7 +35843,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H16" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I16" t="n">
         <v>163.0214951995539</v>
@@ -35931,25 +35931,25 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K17" t="n">
-        <v>175.9119195979899</v>
+        <v>377.6899601296241</v>
       </c>
       <c r="L17" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M17" t="n">
-        <v>490.597359871433</v>
+        <v>649</v>
       </c>
       <c r="N17" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P17" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q17" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36080,13 +36080,13 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H19" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I19" t="n">
         <v>163.0214951995539</v>
       </c>
       <c r="J19" t="n">
-        <v>329.5882314919643</v>
+        <v>329.5882314919611</v>
       </c>
       <c r="K19" t="n">
         <v>104.5500458709881</v>
@@ -36165,16 +36165,16 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>512.6348760697097</v>
+        <v>85.53039583476264</v>
       </c>
       <c r="K20" t="n">
-        <v>175.9119195979899</v>
+        <v>175.91191959799</v>
       </c>
       <c r="L20" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M20" t="n">
-        <v>60.29262328527617</v>
+        <v>649</v>
       </c>
       <c r="N20" t="n">
         <v>649</v>
@@ -36186,7 +36186,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q20" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36417,13 +36417,13 @@
         <v>649</v>
       </c>
       <c r="O23" t="n">
-        <v>162.757678164601</v>
+        <v>165.9579345158106</v>
       </c>
       <c r="P23" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.200256351209361</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36551,10 +36551,10 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G25" t="n">
-        <v>76.5764550273293</v>
+        <v>76.57645502732242</v>
       </c>
       <c r="H25" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I25" t="n">
         <v>163.0214951995539</v>
@@ -36639,7 +36639,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K26" t="n">
         <v>175.9119195979899</v>
@@ -36648,19 +36648,19 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M26" t="n">
-        <v>40.17514405185721</v>
+        <v>649</v>
       </c>
       <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
         <v>649</v>
       </c>
-      <c r="O26" t="n">
-        <v>162.757678164601</v>
-      </c>
       <c r="P26" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q26" t="n">
-        <v>592.3686050224903</v>
+        <v>166.4189064723676</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36791,7 +36791,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H28" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I28" t="n">
         <v>163.0214951995539</v>
@@ -36876,19 +36876,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>82.3301394835529</v>
+        <v>142.1617908122723</v>
       </c>
       <c r="K29" t="n">
-        <v>175.9119195979899</v>
+        <v>175.91191959799</v>
       </c>
       <c r="L29" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M29" t="n">
-        <v>490.597359871433</v>
+        <v>649</v>
       </c>
       <c r="N29" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>162.757678164601</v>
@@ -37113,7 +37113,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K32" t="n">
         <v>175.9119195979899</v>
@@ -37131,10 +37131,10 @@
         <v>162.757678164601</v>
       </c>
       <c r="P32" t="n">
-        <v>198.5777841804241</v>
+        <v>202.2390124881904</v>
       </c>
       <c r="Q32" t="n">
-        <v>433.9659648939237</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37353,25 +37353,25 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K35" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L35" t="n">
-        <v>218.2342914572864</v>
+        <v>341.869854113801</v>
       </c>
       <c r="M35" t="n">
-        <v>40.17514405185721</v>
+        <v>649</v>
       </c>
       <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>649</v>
       </c>
-      <c r="O35" t="n">
-        <v>162.757678164601</v>
-      </c>
       <c r="P35" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q35" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37490,7 +37490,7 @@
         <v>48.27475335195533</v>
       </c>
       <c r="D37" t="n">
-        <v>35.46378194444452</v>
+        <v>35.46378194444451</v>
       </c>
       <c r="E37" t="n">
         <v>40.01909516304346</v>
@@ -37590,19 +37590,19 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K38" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L38" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M38" t="n">
+        <v>4.355038036033999</v>
+      </c>
+      <c r="N38" t="n">
         <v>649</v>
       </c>
-      <c r="N38" t="n">
-        <v>17.50927946942293</v>
-      </c>
       <c r="O38" t="n">
-        <v>162.757678164601</v>
+        <v>649</v>
       </c>
       <c r="P38" t="n">
         <v>198.5777841804241</v>
@@ -37824,22 +37824,22 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K41" t="n">
-        <v>609.8778844919133</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L41" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M41" t="n">
+        <v>342.3308260703579</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
         <v>649</v>
-      </c>
-      <c r="N41" t="n">
-        <v>649</v>
-      </c>
-      <c r="O41" t="n">
-        <v>162.757678164601</v>
       </c>
       <c r="P41" t="n">
         <v>198.5777841804241</v>
@@ -37976,7 +37976,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H43" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I43" t="n">
         <v>163.0214951995539</v>
@@ -38018,7 +38018,7 @@
         <v>170.0754447911158</v>
       </c>
       <c r="V43" t="n">
-        <v>121.8296897838621</v>
+        <v>121.8296897837838</v>
       </c>
       <c r="W43" t="n">
         <v>94.62719016129032</v>
@@ -38064,13 +38064,13 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K44" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L44" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M44" t="n">
-        <v>649</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="N44" t="n">
         <v>649</v>
@@ -38082,7 +38082,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.200256351209361</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38198,7 +38198,7 @@
         <v>33.88619966292134</v>
       </c>
       <c r="C46" t="n">
-        <v>48.27475335204451</v>
+        <v>48.27475335195533</v>
       </c>
       <c r="D46" t="n">
         <v>35.46378194444452</v>
@@ -38213,7 +38213,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H46" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I46" t="n">
         <v>163.0214951995539</v>
